--- a/backtest_runs/20260410_193731/by_symbol/WTL/WTL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/WTL/WTL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>106557.36</v>
@@ -679,7 +679,7 @@
         <v>-7377.030000000006</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>99180.33</v>
@@ -771,7 +771,7 @@
         <v>-819.6700000000008</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>98360.66</v>
@@ -817,7 +817,7 @@
         <v>-3278.680000000003</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>95081.98</v>
@@ -909,7 +909,7 @@
         <v>-2459.010000000002</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>92622.97</v>
@@ -955,7 +955,7 @@
         <v>-1639.340000000002</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>90983.62999999999</v>
@@ -1047,7 +1047,7 @@
         <v>-2459.010000000002</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>93442.64</v>
@@ -1185,7 +1185,7 @@
         <v>-5737.690000000005</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>90983.62999999999</v>
@@ -1277,7 +1277,7 @@
         <v>-2459.010000000002</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>88524.62</v>
@@ -1415,7 +1415,7 @@
         <v>-1639.340000000002</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>90163.95999999999</v>
